--- a/examples/excel/charts/charts-column.xlsx
+++ b/examples/excel/charts/charts-column.xlsx
@@ -3,13 +3,13 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="1-Column Fundamentals" sheetId="2" r:id="R5d1aca14fade4339"/>
-    <x:sheet name="2-Column Variants" sheetId="3" r:id="R505f1f6f8bda4327"/>
-    <x:sheet name="3-Column Styling" sheetId="4" r:id="R16513cf2a09a46c1"/>
-    <x:sheet name="4-Axis &amp; Gridlines" sheetId="5" r:id="R860b6d047b19441f"/>
-    <x:sheet name="5-Labels &amp; Legend" sheetId="6" r:id="R137ae2f9a2f749f1"/>
-    <x:sheet name="6-Effects &amp; Advanced" sheetId="7" r:id="R4874a86427ac4078"/>
-    <x:sheet name="7-Bar Shape &amp; Gap" sheetId="8" r:id="R0b831798a5424ae3"/>
+    <x:sheet name="1-Column Fundamentals" sheetId="2" r:id="R2002c44212d64206"/>
+    <x:sheet name="2-Column Variants" sheetId="3" r:id="R064aa8b79e314547"/>
+    <x:sheet name="3-Column Styling" sheetId="4" r:id="R45b3dcba47d74fe4"/>
+    <x:sheet name="4-Axis &amp; Gridlines" sheetId="5" r:id="R9486f923814c45b4"/>
+    <x:sheet name="5-Labels &amp; Legend" sheetId="6" r:id="R2eae452b8bf948e7"/>
+    <x:sheet name="6-Effects &amp; Advanced" sheetId="7" r:id="Ra1ee5321b6be471b"/>
+    <x:sheet name="7-Bar Shape &amp; Gap" sheetId="8" r:id="R53ddce1ca62349bf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2053,8 +2053,8 @@
       <c:valAx>
         <c:axId val="2"/>
         <c:scaling>
+          <c:logBase val="10"/>
           <c:orientation val="maxMin"/>
-          <c:logBase val="10"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -2861,6 +2861,18 @@
           </c:spPr>
           <c:dLbls>
             <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="3"/>
               <c:tx>
                 <c:rich>
@@ -4016,6 +4028,7 @@
           </c:val>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -4089,6 +4102,15 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="3"/>
         <c:axId val="4"/>
       </c:barChart>
@@ -4185,7 +4207,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="3"/>
-        <c:crosses val="autoZero"/>
+        <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
     </c:plotArea>
@@ -4972,7 +4994,7 @@
             <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
             <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
-                <a:defRPr sz="800" b="0">
+                <a:defRPr sz="800">
                   <a:solidFill>
                     <a:srgbClr val="666666"/>
                   </a:solidFill>
@@ -4980,6 +5002,7 @@
               </a:pPr>
             </a:p>
           </c:txPr>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -5930,9 +5953,10 @@
           </c:val>
         </c:ser>
         <c:gapWidth val="150"/>
+        <c:shape val="cylinder"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-        <c:shape val="cylinder"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -5966,6 +5990,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -6128,9 +6161,10 @@
           </c:val>
         </c:ser>
         <c:gapWidth val="150"/>
+        <c:shape val="cone"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-        <c:shape val="cone"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -6164,6 +6198,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -6216,11 +6259,90 @@
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$B$2:$B$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>188</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>172</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>198</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -6238,11 +6360,90 @@
           <c:cat>
             <c:strRef>
               <c:f>Sheet1!$A$2:$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>Sheet1!$C$2:$C$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>108</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>142</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>158</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
         </c:ser>
@@ -6800,12 +7001,12 @@
           </c:val>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="ctr"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
-          <c:dLblPos val="ctr"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
@@ -7495,6 +7696,7 @@
         <c:gapWidth val="150"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -7528,6 +7730,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
@@ -7754,9 +7965,10 @@
           </c:val>
         </c:ser>
         <c:gapWidth val="150"/>
+        <c:gapDepth val="200"/>
         <c:axId val="1"/>
         <c:axId val="2"/>
-        <c:gapDepth val="200"/>
+        <c:axId val="3"/>
       </c:bar3DChart>
       <c:catAx>
         <c:axId val="1"/>
@@ -7790,6 +8002,15 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:serAx>
+        <c:axId val="3"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:crossAx val="2"/>
+      </c:serAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -8167,7 +8388,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfd7b0909791b4b6f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf7cb9ea2b0a845c3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8197,7 +8418,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4c53b5df53c41c5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0cb3bbee400e4b27"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8227,7 +8448,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7f1cc58965694444"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcf5b4bc3b16c4df4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8257,7 +8478,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23d80f0be6304a79"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re01f1cbcf9d84186"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8292,7 +8513,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d4f9eadabc04a48"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f9a2407ed5d4ce6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8322,7 +8543,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2cbe4303f87b4648"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd8362c3c4c7744ce"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8352,7 +8573,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdac9fc4346064979"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re2d73016b85f4a35"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8382,7 +8603,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d6c26c776d5494b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R582baafa6de945d5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8417,7 +8638,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R753ff7071b7047b0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R80aadc3204be41c1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8447,7 +8668,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8348c262320e43f4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14997c5b371149a2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8477,7 +8698,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R72a9787856d14793"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb97ae1fcb80d4198"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8507,7 +8728,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1fd7c85e03d7417d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9b9a2784a7754f19"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8542,7 +8763,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc9e61bc44d4b484a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra48b5ef8ac294e22"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8572,7 +8793,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R99c77850e47e418c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2c3cbafa92ca40af"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8602,7 +8823,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re50d8854d16741f9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R11a9d4249fe840c9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8632,7 +8853,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf8b5a90cfb994bb9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref0aa570b33c4e39"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8667,7 +8888,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9aa1e04211814b59"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9ccfd758309a492a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8697,7 +8918,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdaf7a7ec94724f7e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R314ed4e0163b40ed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8727,7 +8948,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64346e82d3404c1b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R14ab7dda99e840fc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8757,7 +8978,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfa4aaccdcf1f4ad3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R753c7056364f4503"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8792,7 +9013,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd3248784d18d4a7e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2799ac738d584379"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8822,7 +9043,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R527e83e9733a4cc8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R31a4d378b1114c95"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8852,7 +9073,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R10b552b8f82945be"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf66d0411b0dc4eab"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8882,7 +9103,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9a13915f081c4736"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5799da9f1bc14ce1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8917,7 +9138,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb01d86320ac24d03"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7cb9379bd2884168"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8947,7 +9168,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23bf023cdd4b4726"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R96851cd5df254a37"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -8977,7 +9198,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R401e8853ac4146f2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8bb9e1334360426e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -9007,13 +9228,122 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0bf897b91fbc4b29"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R711bf21ecd894b7e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9247,48 +9577,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b83545d3b0f43ba"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24b57aea57354924"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R508bf5dab7d84c6b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56f4f6617d6249c9"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R874f96e607774c48"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ece764f4c7341ae"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5243e3d007594cc3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ac5b39d88f842f7"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra980c2a54c4c4fbe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb13210a58f044f0c"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb79393c223d140fe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8090835c66d94bd6"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14e95b0967a441f0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b516475955049d3"/>
 </x:worksheet>
 </file>